--- a/港岛-黄泥涌-蓝塘道23-39号/蓝塘道23-39号_销控明细表.xlsx
+++ b/港岛-黄泥涌-蓝塘道23-39号/蓝塘道23-39号_销控明细表.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2016-12-14</t>
+          <t>2016-12-15</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -942,7 +942,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2019-05-13</t>
+          <t>2019-05-14</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2018-06-11</t>
+          <t>2018-06-12</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2018-04-11</t>
+          <t>2018-04-12</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2018-04-18</t>
+          <t>2018-04-19</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-02-09</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2019-05-13</t>
+          <t>2019-05-14</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2019-03-19</t>
+          <t>2019-03-20</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2018-02-26</t>
+          <t>2018-02-27</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2016-10-17</t>
+          <t>2016-10-18</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2021-07-25</t>
+          <t>2021-07-26</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -2077,7 +2077,7 @@
         <is>
           <t>A号屋 (蓝塘道25号)
 4575呎 (4+房)
-(16年-12月-14日)
+(16年-12月-15日)
 $3.02亿
 $65,967/呎</t>
         </is>
@@ -2086,7 +2086,7 @@
         <is>
           <t>A号屋 (蓝塘道27号)
 4575呎 (4+房)
-(18年-06月-11日)
+(18年-06月-12日)
 $3.06亿
 $66,842/呎</t>
         </is>
@@ -2095,7 +2095,7 @@
         <is>
           <t>A号屋 (蓝塘道29号)
 4575呎 (4+房)
-(18年-04月-18日)
+(18年-04月-19日)
 $3.28亿
 $71,694/呎</t>
         </is>
@@ -2104,7 +2104,7 @@
         <is>
           <t>A号屋 (蓝塘道31号)
 4575呎 (1房)
-(25年-12月-31日)
+(26年-01月-01日)
 $4.47亿
 $97,747/呎</t>
         </is>
@@ -2113,7 +2113,7 @@
         <is>
           <t>A号屋 (蓝塘道33号)
 4575呎 (4+房)
-(25年-12月-21日)
+(25年-12月-22日)
 $2.28亿
 $49,810/呎</t>
         </is>
@@ -2131,7 +2131,7 @@
         <is>
           <t>A号屋 (蓝塘道37号)
 4575呎 (4+房)
-(19年-03月-19日)
+(19年-03月-20日)
 $3.38亿
 $73,923/呎</t>
         </is>
@@ -2140,7 +2140,7 @@
         <is>
           <t>A号屋 (蓝塘道39号)
 4575呎 (4+房)
-(16年-10月-17日)
+(16年-10月-18日)
 $2.88亿
 $63,016/呎</t>
         </is>
@@ -2165,7 +2165,7 @@
         <is>
           <t>B号屋 (蓝塘道25号)
 4602呎 (4+房)
-(19年-05月-13日)
+(19年-05月-14日)
 $3.34亿
 $72,534/呎</t>
         </is>
@@ -2174,7 +2174,7 @@
         <is>
           <t>B号屋 (蓝塘道27号)
 4602呎 (4+房)
-(18年-04月-11日)
+(18年-04月-12日)
 $3.38亿
 $73,490/呎</t>
         </is>
@@ -2183,7 +2183,7 @@
         <is>
           <t>B号屋 (蓝塘道29号)
 4602呎 (4+房)
-(24年-06月-04日)
+(24年-06月-05日)
 $2.50亿
 $54,324/呎</t>
         </is>
@@ -2192,7 +2192,7 @@
         <is>
           <t>B号屋 (蓝塘道31号)
 4602呎 (1房)
-(25年-12月-31日)
+(26年-01月-01日)
 $4.47亿
 $97,173/呎</t>
         </is>
@@ -2201,7 +2201,7 @@
         <is>
           <t>B号屋 (蓝塘道33号)
 4602呎 (4+房)
-(24年-02月-08日)
+(24年-02月-09日)
 $2.30亿
 $49,978/呎</t>
         </is>
@@ -2210,7 +2210,7 @@
         <is>
           <t>B号屋 (蓝塘道35号)
 4602呎 (4+房)
-(19年-05月-13日)
+(19年-05月-14日)
 $3.34亿
 $72,534/呎</t>
         </is>
@@ -2219,7 +2219,7 @@
         <is>
           <t>B号屋 (蓝塘道37号)
 4602呎 (4+房)
-(18年-02月-26日)
+(18年-02月-27日)
 $3.04亿
 $66,015/呎</t>
         </is>
@@ -2228,7 +2228,7 @@
         <is>
           <t>B号屋 (蓝塘道39号)
 4602呎 (3房)
-(21年-07月-25日)
+(21年-07月-26日)
 $3.40亿
 $73,837/呎</t>
         </is>
